--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_magallanes.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:28</t>
+    <t xml:space="preserve">2026-09-24 01:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -634,7 +634,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -674,7 +674,7 @@
         <v>0.37</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.28</v>
@@ -824,13 +824,13 @@
         <v>16</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="15">
@@ -847,13 +847,13 @@
         <v>16</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="16">
@@ -870,13 +870,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -893,13 +893,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.56</v>
+        <v>-0.51</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.73</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="18">
@@ -964,7 +964,7 @@
         <v>-0.35</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="21">
@@ -981,13 +981,13 @@
         <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.45</v>
+        <v>0.46</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.13</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.36</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="22">
@@ -1004,13 +1004,13 @@
         <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.55</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="23">
@@ -1027,13 +1027,13 @@
         <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>-0.19</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="24">
@@ -1194,7 +1194,7 @@
         <v>0.49</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0.57</v>
@@ -1298,13 +1298,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="37">
@@ -1321,13 +1321,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.05</v>
+        <v>0.46</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.15</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="38">
@@ -1344,13 +1344,13 @@
         <v>16</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="39">
@@ -1367,13 +1367,13 @@
         <v>16</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.22</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="40">
@@ -1415,7 +1415,7 @@
         <v>-0.35</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="42">
@@ -1455,13 +1455,13 @@
         <v>33</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="44">
@@ -1478,13 +1478,13 @@
         <v>33</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.53</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="45">
@@ -1501,13 +1501,13 @@
         <v>33</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>-0.11</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="46">
@@ -1929,13 +1929,13 @@
         <v>33</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.37</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.12</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="66">
@@ -1952,13 +1952,13 @@
         <v>33</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="67">
@@ -1975,13 +1975,13 @@
         <v>33</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:18</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_magallanes.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
